--- a/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/18_operational_process_evidence.xlsx
+++ b/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/18_operational_process_evidence.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R60a99c83c90e4f39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Rcd181dd857a541b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R3fc53b7e41c3418e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R7d9b63a6811a4d05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R377a81a64f314a62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R014580a632614445"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R6954a9b4455b467d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R0c3563f72931481c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R8181d12a8d524aea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Rbb7beaacd0974d94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R9689af0420624e59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Rf9c3d5cd1e2c4618"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -628,7 +628,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re68636e3bef34c29"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1733d041a0db491c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -809,7 +809,7 @@
         <x:v>HARBORTRUST-BANK-HT-ENTERPRISE-EV01; HARBORTRUST-BANK-HT-ENTERPRISE-EV02</x:v>
       </x:c>
       <x:c r="O6" s="78" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Validate Executive Office evidence and readiness workflow (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for operational process evidence.</x:v>
       </x:c>
       <x:c r="P6" s="41" t="str">
         <x:v>High</x:v>
@@ -859,7 +859,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-EV01; HARBORTRUST-BANK-HT-RETAIL-EV02</x:v>
       </x:c>
       <x:c r="O7" s="79" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Confirm Retail Deposits and Branch Operations evidence and readiness workflow (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this operational process evidence record is used downstream.</x:v>
       </x:c>
       <x:c r="P7" s="45" t="str">
         <x:v>High</x:v>
@@ -909,7 +909,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMMERCIAL-EV01; HARBORTRUST-BANK-HT-COMMERCIAL-EV02</x:v>
       </x:c>
       <x:c r="O8" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Attach client evidence for Commercial Lending and Treasury evidence and readiness workflow (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P8" t="str">
         <x:v>High</x:v>
@@ -959,7 +959,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-EV01; HARBORTRUST-BANK-HT-CARDS-EV02</x:v>
       </x:c>
       <x:c r="O9" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Reconcile Cards Operations evidence and readiness workflow (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P9" t="str">
         <x:v>High</x:v>
@@ -1009,7 +1009,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-EV01; HARBORTRUST-BANK-HT-PAYMENTS-EV02</x:v>
       </x:c>
       <x:c r="O10" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Payments Operations evidence and readiness workflow (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P10" t="str">
         <x:v>High</x:v>
@@ -1059,7 +1059,7 @@
         <x:v>HARBORTRUST-BANK-HT-LENDING-EV01; HARBORTRUST-BANK-HT-LENDING-EV02</x:v>
       </x:c>
       <x:c r="O11" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Validate Consumer Lending Operations evidence and readiness workflow (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for operational process evidence.</x:v>
       </x:c>
       <x:c r="P11" t="str">
         <x:v>High</x:v>
@@ -1109,7 +1109,7 @@
         <x:v>HARBORTRUST-BANK-HT-WEALTH-EV01; HARBORTRUST-BANK-HT-WEALTH-EV02</x:v>
       </x:c>
       <x:c r="O12" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Confirm Wealth Advisory and Brokerage evidence and readiness workflow (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this operational process evidence record is used downstream.</x:v>
       </x:c>
       <x:c r="P12" t="str">
         <x:v>High</x:v>
@@ -1147,19 +1147,19 @@
         <x:v>Known source inventory and owner context exist in candidate pack.</x:v>
       </x:c>
       <x:c r="K13" t="str">
-        <x:v>Automate evidence intake, relationship projection, data quality checks, and module context packets.</x:v>
+        <x:v>fraud analyst copilot with cited case packet; feature-store feedback loop; model-risk-approved evaluation set.</x:v>
       </x:c>
       <x:c r="L13" t="str">
-        <x:v>Relationship depth and measured outcomes must be validated before high-stakes claims.</x:v>
+        <x:v>case outcome feedback gaps; model version lineage gaps; queue aging mixed with model quality signals.</x:v>
       </x:c>
       <x:c r="M13" t="str">
         <x:v>Evidence lineage, privacy/security review, source approval, and operator promotion gate required.</x:v>
       </x:c>
       <x:c r="N13" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-RISK-EV01; HARBORTRUST-BANK-HT-FRAUD-RISK-EV02</x:v>
+        <x:v>Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields.; Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status.; AML transaction monitoring source inventory and control-owner interview.; Digital onboarding/KYC vendor report with identity verification and device-risk signals.; Fraud feature store design notes with feedback-loop and model governance gaps.</x:v>
       </x:c>
       <x:c r="O13" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Validate Fraud and Risk Operations evidence and readiness workflow (record 8) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P13" t="str">
         <x:v>High</x:v>
@@ -1209,7 +1209,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMPLIANCE-EV01; HARBORTRUST-BANK-HT-COMPLIANCE-EV02</x:v>
       </x:c>
       <x:c r="O14" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Reconcile Compliance and Model Risk Management evidence and readiness workflow (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P14" t="str">
         <x:v>High</x:v>
@@ -1259,7 +1259,7 @@
         <x:v>HARBORTRUST-BANK-HT-CONTACT-CENTER-EV01; HARBORTRUST-BANK-HT-CONTACT-CENTER-EV02</x:v>
       </x:c>
       <x:c r="O15" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Contact Center and Servicing evidence and readiness workflow (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P15" t="str">
         <x:v>High</x:v>
@@ -1309,7 +1309,7 @@
         <x:v>HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV01; HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV02</x:v>
       </x:c>
       <x:c r="O16" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Validate Digital Account Opening and Onboarding evidence and readiness workflow (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for operational process evidence.</x:v>
       </x:c>
       <x:c r="P16" t="str">
         <x:v>High</x:v>
@@ -1359,7 +1359,7 @@
         <x:v>HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV01; HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV02</x:v>
       </x:c>
       <x:c r="O17" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Confirm Core Banking Modernization evidence and readiness workflow (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this operational process evidence record is used downstream.</x:v>
       </x:c>
       <x:c r="P17" t="str">
         <x:v>High</x:v>
@@ -1409,7 +1409,7 @@
         <x:v>HARBORTRUST-BANK-HT-CUSTOMER-360-EV01; HARBORTRUST-BANK-HT-CUSTOMER-360-EV02</x:v>
       </x:c>
       <x:c r="O18" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Attach client evidence for Customer 360 Data Product evidence and readiness workflow (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P18" t="str">
         <x:v>High</x:v>
@@ -1459,7 +1459,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV01; HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV02</x:v>
       </x:c>
       <x:c r="O19" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Reconcile Retail Banking Analytics evidence and readiness workflow (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P19" t="str">
         <x:v>High</x:v>
@@ -1509,7 +1509,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV01; HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV02</x:v>
       </x:c>
       <x:c r="O20" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cards Portfolio Analytics evidence and readiness workflow (record 15) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P20" t="str">
         <x:v>High</x:v>
@@ -1559,7 +1559,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV01; HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV02</x:v>
       </x:c>
       <x:c r="O21" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Validate Payments and Settlement Analytics evidence and readiness workflow (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for operational process evidence.</x:v>
       </x:c>
       <x:c r="P21" t="str">
         <x:v>High</x:v>
@@ -1597,19 +1597,19 @@
         <x:v>Known source inventory and owner context exist in candidate pack.</x:v>
       </x:c>
       <x:c r="K22" t="str">
-        <x:v>Automate evidence intake, relationship projection, data quality checks, and module context packets.</x:v>
+        <x:v>fraud analyst copilot with cited case packet; feature-store feedback loop; model-risk-approved evaluation set.</x:v>
       </x:c>
       <x:c r="L22" t="str">
-        <x:v>Relationship depth and measured outcomes must be validated before high-stakes claims.</x:v>
+        <x:v>case outcome feedback gaps; model version lineage gaps; queue aging mixed with model quality signals.</x:v>
       </x:c>
       <x:c r="M22" t="str">
         <x:v>Evidence lineage, privacy/security review, source approval, and operator promotion gate required.</x:v>
       </x:c>
       <x:c r="N22" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV01; HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV02</x:v>
+        <x:v>Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields.; Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status.; AML transaction monitoring source inventory and control-owner interview.; Digital onboarding/KYC vendor report with identity verification and device-risk signals.; Fraud feature store design notes with feedback-loop and model governance gaps.</x:v>
       </x:c>
       <x:c r="O22" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Validate Fraud and Risk Analytics evidence and readiness workflow (record 17) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P22" t="str">
         <x:v>High</x:v>
@@ -1659,7 +1659,7 @@
         <x:v>HARBORTRUST-BANK-HT-DATA-PLATFORM-EV01; HARBORTRUST-BANK-HT-DATA-PLATFORM-EV02</x:v>
       </x:c>
       <x:c r="O23" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Attach client evidence for Cloud Data Platform evidence and readiness workflow (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P23" t="str">
         <x:v>High</x:v>
@@ -1709,7 +1709,7 @@
         <x:v>HARBORTRUST-BANK-HT-IT-BUDGET-EV01; HARBORTRUST-BANK-HT-IT-BUDGET-EV02</x:v>
       </x:c>
       <x:c r="O24" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Reconcile IT Budget and Tower Baseline evidence and readiness workflow (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P24" t="str">
         <x:v>High</x:v>
@@ -1759,7 +1759,7 @@
         <x:v>HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV01; HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV02</x:v>
       </x:c>
       <x:c r="O25" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor and Contract Optimization evidence and readiness workflow (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P25" t="str">
         <x:v>High</x:v>
@@ -1809,7 +1809,7 @@
         <x:v>HARBORTRUST-BANK-HT-CMDB-INFRA-EV01; HARBORTRUST-BANK-HT-CMDB-INFRA-EV02</x:v>
       </x:c>
       <x:c r="O26" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Validate Infrastructure and CMDB evidence and readiness workflow (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for operational process evidence.</x:v>
       </x:c>
       <x:c r="P26" t="str">
         <x:v>High</x:v>
@@ -1859,7 +1859,7 @@
         <x:v>HARBORTRUST-BANK-HT-INCIDENTS-EV01; HARBORTRUST-BANK-HT-INCIDENTS-EV02</x:v>
       </x:c>
       <x:c r="O27" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Confirm Incident Problem Change Operations evidence and readiness workflow (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this operational process evidence record is used downstream.</x:v>
       </x:c>
       <x:c r="P27" t="str">
         <x:v>High</x:v>
@@ -1877,7 +1877,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98b64014b794405c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95b9ffd75acf4351"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1952,7 +1952,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c40baa17f504909"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec008ee651db49d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2146,7 +2146,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18360fe5d94947d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3afbc4a045134f6b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2200,7 +2200,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f6e827f7dcc4bbe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R515bc72993b341fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2310,7 +2310,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra129986c5c6e46dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fa8d0b92e024ad8"/>
   </x:tableParts>
 </x:worksheet>
 </file>